--- a/pseudodata/1010.xlsx
+++ b/pseudodata/1010.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,24 +536,24 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000732912172919014</v>
+        <v>0.0002048600017658673</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001186280533320948</v>
+        <v>0.0005111386974381369</v>
       </c>
       <c r="N2" t="n">
-        <v>3.66456086459507e-05</v>
+        <v>1.024300008829336e-05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -590,24 +590,24 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009028821527122683</v>
+        <v>0.0001815240846669416</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001599085683533111</v>
+        <v>0.0005205574247845207</v>
       </c>
       <c r="N3" t="n">
-        <v>4.514410763561342e-05</v>
+        <v>9.076204233347079e-06</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -644,24 +644,24 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008517570351968822</v>
+        <v>0.0001356720240446564</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002254115813736962</v>
+        <v>0.0005694603858978065</v>
       </c>
       <c r="N4" t="n">
-        <v>4.258785175984411e-05</v>
+        <v>6.783601202232819e-06</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,24 +698,24 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000675204108927668</v>
+        <v>6.925304189431206e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0003213131265680984</v>
+        <v>0.0006626667106961018</v>
       </c>
       <c r="N5" t="n">
-        <v>3.37602054463834e-05</v>
+        <v>3.462652094715603e-06</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -752,24 +752,24 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004236826151968522</v>
+        <v>-1.488895647091454e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004577130019222242</v>
+        <v>0.0008112087937481722</v>
       </c>
       <c r="N6" t="n">
-        <v>2.118413075984261e-05</v>
+        <v>-7.444478235457272e-07</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -806,24 +806,24 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001314971968988704</v>
+        <v>-0.000110454193613701</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0006347392515247521</v>
+        <v>0.001031664732270719</v>
       </c>
       <c r="N7" t="n">
-        <v>6.574859844943523e-06</v>
+        <v>-5.52270968068505e-06</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -860,24 +860,24 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001246453898194211</v>
+        <v>-0.0002060229895529169</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0008369550755115968</v>
+        <v>0.001345773520113073</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.232269490971055e-06</v>
+        <v>-1.030114947764584e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -908,30 +908,30 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.000104461378325654</v>
+        <v>-0.0002848026375878743</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001186280533320948</v>
+        <v>0.001780678425406445</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.223068916282702e-06</v>
+        <v>-1.424013187939372e-05</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -962,30 +962,30 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>6.423878474667353e-05</v>
+        <v>-0.0003259749688812096</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001599085683533111</v>
+        <v>0.002369726654090828</v>
       </c>
       <c r="N10" t="n">
-        <v>3.211939237333677e-06</v>
+        <v>-1.629874844406048e-05</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1016,30 +1016,30 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001876325197905747</v>
+        <v>-0.0003087085067055127</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002254115813736962</v>
+        <v>0.003149576875420136</v>
       </c>
       <c r="N11" t="n">
-        <v>9.381625989528736e-06</v>
+        <v>-1.543542533527564e-05</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1070,30 +1070,30 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000248773330653805</v>
+        <v>-0.0002201316738730216</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0003213131265680984</v>
+        <v>0.004144622107752479</v>
       </c>
       <c r="N12" t="n">
-        <v>1.243866653269025e-05</v>
+        <v>-1.100658369365108e-05</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1124,30 +1124,30 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K13" t="n">
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000257060359501941</v>
+        <v>-6.085910510374354e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0004577130019222242</v>
+        <v>0.005339920922452969</v>
       </c>
       <c r="N13" t="n">
-        <v>1.285301797509705e-05</v>
+        <v>-3.042955255187177e-06</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1178,30 +1178,30 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002206183857275422</v>
+        <v>0.0001691152499128881</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0006347392515247521</v>
+        <v>0.006682539066461773</v>
       </c>
       <c r="N14" t="n">
-        <v>1.103091928637711e-05</v>
+        <v>8.455762495644406e-06</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1232,30 +1232,30 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001679523754007734</v>
+        <v>0.0004965919765267876</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0008369550755115968</v>
+        <v>0.008155634095145376</v>
       </c>
       <c r="N15" t="n">
-        <v>8.397618770038669e-06</v>
+        <v>2.482959882633938e-05</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1286,30 +1286,30 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>1.236351105245078e-06</v>
+        <v>0.0009636365821541357</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001186280533320948</v>
+        <v>0.009851105147122917</v>
       </c>
       <c r="N16" t="n">
-        <v>6.181755526225391e-08</v>
+        <v>4.818182910770678e-05</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1340,30 +1340,30 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.488908685336508e-05</v>
+        <v>0.001569211868426151</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001599085683533111</v>
+        <v>0.01191789723799614</v>
       </c>
       <c r="N17" t="n">
-        <v>-7.444543426682542e-07</v>
+        <v>7.846059342130757e-05</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1394,30 +1394,30 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
+          <t>cos(phi_kp)</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.993812320315659e-06</v>
+        <v>0.002212532742392742</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0002254115813736962</v>
+        <v>0.01439608613482353</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.996906160157829e-07</v>
+        <v>0.0001106266371196371</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1425,222 +1425,6 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.303799651020565e-05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0003213131265680984</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.151899825510283e-06</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.327029464978539e-05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0004577130019222242</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.163514732489269e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0001025105002842511</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0006347392515247521</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.125525014212558e-06</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.0001390937322778411</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0008369550755115968</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.954686613892053e-06</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
         <v>1</v>
       </c>
     </row>
